--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -1,57 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -66,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,93 +420,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F2" t="n">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G2" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E2">
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1">
+      <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
         <v>12</v>
       </c>
-      <c r="C5">
+      <c r="E5" t="n">
         <v>13</v>
       </c>
-      <c r="D5">
+      <c r="F5" t="n">
         <v>14</v>
       </c>
-      <c r="E5">
+      <c r="G5" t="n">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,36 +425,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -474,12 +484,18 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -494,15 +510,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -517,15 +539,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>10</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -540,15 +568,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
         <v>12</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>13</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>14</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,46 +425,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.4</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -490,12 +495,15 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -516,15 +524,18 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>5</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -545,15 +556,18 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
         <v>8</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>9</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -574,15 +588,18 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
         <v>12</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>13</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>14</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -425,51 +425,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.5</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -498,12 +503,15 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -527,15 +535,18 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -559,15 +570,18 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -591,15 +605,18 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>12</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>13</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -425,56 +425,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.6</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -506,12 +511,15 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -538,15 +546,18 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -573,15 +584,18 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>8</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>10</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -608,15 +622,18 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
         <v>12</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>13</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>14</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -425,61 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.8</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.7</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -514,12 +524,18 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -549,15 +565,21 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -587,15 +609,21 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>10</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -625,15 +653,21 @@
         <v>3</v>
       </c>
       <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>12</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>13</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>14</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,71 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.9</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -530,12 +535,15 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -571,15 +579,18 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>6</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -615,15 +626,18 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
         <v>8</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>9</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>10</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -659,15 +673,18 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
         <v>12</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>13</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>14</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,76 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.10</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -538,12 +543,15 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -582,15 +590,18 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>4</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -629,15 +640,18 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
         <v>8</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>9</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>10</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -676,15 +690,18 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
         <v>12</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>13</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>14</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,81 +425,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.11</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.10</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -546,12 +551,15 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -593,15 +601,18 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
         <v>4</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>5</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -643,15 +654,18 @@
         <v>2</v>
       </c>
       <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
         <v>8</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>9</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>10</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -693,15 +707,18 @@
         <v>3</v>
       </c>
       <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
         <v>12</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>13</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>14</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,86 +425,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.12</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.11</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.10</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -554,12 +559,15 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -604,15 +612,18 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
         <v>4</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>5</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -657,15 +668,18 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
         <v>8</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>9</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -710,15 +724,18 @@
         <v>3</v>
       </c>
       <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
         <v>12</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>13</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>14</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>15</v>
       </c>
     </row>

--- a/data/Excel_Sample.xlsx
+++ b/data/Excel_Sample.xlsx
@@ -425,91 +425,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.13</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.12</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.11</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.10</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -562,12 +567,15 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -615,15 +623,18 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
         <v>4</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>5</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>6</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -671,15 +682,18 @@
         <v>2</v>
       </c>
       <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
         <v>8</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>10</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -727,15 +741,18 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
         <v>12</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>13</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>14</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>15</v>
       </c>
     </row>
